--- a/rules/CORE-000767/positive/01/data/unit-test-CG0603-positive_seq.xlsx
+++ b/rules/CORE-000767/positive/01/data/unit-test-CG0603-positive_seq.xlsx
@@ -2485,7 +2485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2780,6 +2780,66 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AESEQ</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AECM-GUARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CMSEQ</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AECM-GUARD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rules/CORE-000767/positive/01/data/unit-test-CG0603-positive_seq.xlsx
+++ b/rules/CORE-000767/positive/01/data/unit-test-CG0603-positive_seq.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1226,91 @@
           <t>2013-05-20</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>IBUPROFEN</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Ibuprofen</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>CONCOMITANT THERAPY</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS THERAPY</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="inlineStr">
+        <is>
+          <t>2013-04-29</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="T8" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1947,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2471,6 +2556,72 @@
         </is>
       </c>
       <c r="Q7" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>OCCUR</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Occurrence Indicator</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>IBUPROFEN</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>2012-12-02</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2485,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2840,6 +2991,56 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FASEQ</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CMFA-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CMSEQ</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CMFA-3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
